--- a/Dataset.xlsx
+++ b/Dataset.xlsx
@@ -272,7 +272,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Khmer OS Siemreap"/>
       <family val="2"/>
     </font>
@@ -318,7 +318,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -346,9 +346,6 @@
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -666,9 +663,9 @@
     <col min="3" max="3" style="9" width="15.576428571428572" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="9" width="15.576428571428572" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="10" width="24.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="11" width="18.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="12" width="18.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="12" width="22.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="10" width="18.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="11" width="18.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="11" width="22.719285714285714" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="21">
@@ -1165,7 +1162,7 @@
         <v>47488737</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="21">
       <c r="A20" s="4">
         <v>2023</v>
       </c>
